--- a/outputs/2026-01-30/generic_duplicate_summary.xlsx
+++ b/outputs/2026-01-30/generic_duplicate_summary.xlsx
@@ -446,7 +446,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Entity Count</t>
+          <t>Entity_Count</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10080432115999</t>
+          <t>50224636501228</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -641,17 +641,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Classic_Drinks, Menigo, Sysco_Northern_Ireland</t>
+          <t>Brakes, Fresh_Direct</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>8710679121334</t>
+          <t>10080432115999</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -659,7 +659,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brakes, Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Classic_Drinks, Menigo, Sysco_Northern_Ireland</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -669,7 +669,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>50224636501228</t>
+          <t>8710679121334</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -677,17 +677,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brakes, Fresh_Direct</t>
+          <t>Brakes, Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5099057887318</t>
+          <t>05098878016617</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -705,7 +705,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5099057887349</t>
+          <t>5099057887318</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -723,7 +723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5099057887332</t>
+          <t>5060192824780</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes, Fresh_Direct</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -741,7 +741,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5099057887325</t>
+          <t>5010421174520</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -749,17 +749,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Brakes</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5099057887356</t>
+          <t>4003669016210</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -767,7 +767,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sysco_Northern_Ireland, Sysco_ROI</t>
+          <t>Menigo, Sysco_Northern_Ireland</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -777,7 +777,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5099057887387</t>
+          <t>05016236034981</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -795,7 +795,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4003669016210</t>
+          <t>0501028510829</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -803,7 +803,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Menigo, Sysco_Northern_Ireland</t>
+          <t>Brakes, Fresh_Direct</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -813,7 +813,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5099057887370</t>
+          <t>5099057887325</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -831,7 +831,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5099057887363</t>
+          <t>5099057887332</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -849,7 +849,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05016236034981</t>
+          <t>5391542913121</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -867,7 +867,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0501028510829</t>
+          <t>5099057887387</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -875,7 +875,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brakes, Fresh_Direct</t>
+          <t>Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -885,7 +885,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5010421174520</t>
+          <t>5099057887370</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -893,17 +893,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Brakes</t>
+          <t>Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5060192824780</t>
+          <t>5099057887363</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -911,7 +911,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brakes, Fresh_Direct</t>
+          <t>Sysco_Northern_Ireland, Sysco_ROI</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -921,7 +921,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05098878016617</t>
+          <t>5099057887356</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -939,7 +939,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5391542914241</t>
+          <t>5099057887349</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -975,7 +975,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5391542913121</t>
+          <t>5391542914241</t>
         </is>
       </c>
       <c r="B31" t="n">
